--- a/backtest_runs/20260410_193731/by_symbol/IDSM/IDSM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/IDSM/IDSM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-3904.040000000002</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>96095.95999999999</v>
@@ -633,7 +633,7 @@
         <v>-1016.119999999988</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>95079.84000000001</v>
@@ -679,7 +679,7 @@
         <v>-9412.480000000009</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>85667.36</v>
@@ -909,7 +909,7 @@
         <v>-7380.239999999994</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>87271.76000000001</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>87271.76000000001</v>
@@ -1001,7 +1001,7 @@
         <v>-1176.559999999994</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>86095.20000000001</v>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>92994.12000000001</v>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>92994.12000000001</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>92994.12000000001</v>
